--- a/references/source-data/拓普报价表.xlsx
+++ b/references/source-data/拓普报价表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/856cf0a02f297490/桌面/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\50428\OneDrive\桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC9E053D-3B4F-4A86-9862-72DDB6FCCFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0E95E7-B8F1-4C20-B237-E82860EF7B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7590" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品成本统计" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="87">
   <si>
     <t>产品编码</t>
   </si>
@@ -328,6 +328,18 @@
   </si>
   <si>
     <t>亚克力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DYX-BX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可选</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -699,18 +711,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="2" max="3" width="13.6328125" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="19.26953125" customWidth="1"/>
-    <col min="13" max="13" width="11.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.25" customWidth="1"/>
+    <col min="13" max="13" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,7 +763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -786,7 +798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -821,7 +833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -859,7 +871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -894,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -932,12 +944,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>36</v>
@@ -949,13 +961,13 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>11</v>
@@ -967,12 +979,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>36</v>
@@ -984,13 +996,13 @@
         <v>7</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
       </c>
       <c r="H8">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>11</v>
@@ -1002,12 +1014,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>36</v>
@@ -1019,13 +1031,13 @@
         <v>7</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>11</v>
@@ -1037,12 +1049,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>36</v>
@@ -1054,13 +1066,13 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
         <v>8</v>
       </c>
       <c r="H10">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>11</v>
@@ -1072,12 +1084,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>36</v>
@@ -1089,27 +1101,30 @@
         <v>7</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
         <v>8</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>26</v>
@@ -1124,27 +1139,30 @@
         <v>7</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
         <v>8</v>
       </c>
       <c r="H12">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1159,36 +1177,36 @@
         <v>7</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
         <v>8</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -1197,36 +1215,36 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
         <v>8</v>
       </c>
       <c r="H14">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -1235,13 +1253,13 @@
         <v>7</v>
       </c>
       <c r="F15">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
         <v>8</v>
       </c>
       <c r="H15">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>11</v>
@@ -1253,82 +1271,6 @@
         <v>15</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16">
-        <v>37</v>
-      </c>
-      <c r="G16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16">
-        <v>34</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17">
-        <v>18</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M17" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1342,13 +1284,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6093C5C-B17D-42A6-B5C1-BA364EA3BE1C}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
@@ -1365,7 +1307,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>68</v>
       </c>
@@ -1382,7 +1324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
@@ -1401,7 +1343,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -1420,7 +1362,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
@@ -1437,7 +1379,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>77</v>
       </c>
@@ -1454,7 +1396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
@@ -1471,7 +1413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>81</v>
       </c>
@@ -1485,7 +1427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>82</v>
       </c>
@@ -1510,15 +1452,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D723ABF0-CCFC-40DE-A4C7-C6E4391C7C14}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="1" max="1" width="9.625" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +1480,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -1555,7 +1497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1572,7 +1514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -1589,7 +1531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1603,10 +1545,10 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -1623,7 +1565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -1637,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -1657,7 +1599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1671,7 +1613,24 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
